--- a/public/Dhulfiqar_Scouts_Leader_Logins.xlsx
+++ b/public/Dhulfiqar_Scouts_Leader_Logins.xlsx
@@ -4,24 +4,30 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Leader &amp; Assistant Logins" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Leader &amp; Ṭalīʿah Logins" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="118">
-  <si>
-    <t>⚜️ Dhulfiqār Scouts — Leader &amp; Assistant Login Credentials</t>
-  </si>
-  <si>
-    <t>Portal URL: http://localhost:5173 | Default Password for All Accounts: scouts2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="144">
+  <si>
+    <t>⚜️ Dhulfiqār Scouts — Leader &amp; Ṭalīʿah (Group) Login Credentials</t>
+  </si>
+  <si>
+    <t>Universal Mobile App: http://localhost:5173 | Default Password for All Accounts: scouts2026</t>
   </si>
   <si>
     <t>Grade / Patrol Unit</t>
   </si>
   <si>
+    <t>Ṭalīʿah Rank</t>
+  </si>
+  <si>
+    <t>Ṭalīʿah Group Name</t>
+  </si>
+  <si>
     <t>Role</t>
   </si>
   <si>
@@ -46,6 +52,12 @@
     <t>All Units (Admin)</t>
   </si>
   <si>
+    <t>Troop Command</t>
+  </si>
+  <si>
+    <t>All Troop Units (11 Ṭalāʾiʿ)</t>
+  </si>
+  <si>
     <t>Admin</t>
   </si>
   <si>
@@ -61,7 +73,7 @@
     <t>leader@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>Full admin access to all grades &amp; sessions</t>
+    <t>Full admin access to all grades, ṭalāʾiʿ &amp; sessions</t>
   </si>
   <si>
     <t>Troop Admin</t>
@@ -76,6 +88,12 @@
     <t>Kindergarten</t>
   </si>
   <si>
+    <t>Lions - KG</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat al-Mahdi (ʿaj)</t>
+  </si>
+  <si>
     <t>Leader</t>
   </si>
   <si>
@@ -94,6 +112,12 @@
     <t>1st Grade</t>
   </si>
   <si>
+    <t>Tigers - 1st</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat al-Muṣṭafā (ṣ)</t>
+  </si>
+  <si>
     <t>Nader Chamseddine</t>
   </si>
   <si>
@@ -124,6 +148,12 @@
     <t>2nd Grade</t>
   </si>
   <si>
+    <t>Wolf - 2nd</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat aṣ-Ṣādiq (ʿa)</t>
+  </si>
+  <si>
     <t>Jawad Hazime</t>
   </si>
   <si>
@@ -151,6 +181,12 @@
     <t>3rd Grade</t>
   </si>
   <si>
+    <t>Bear - 3rd</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat ar-Riḍā (ʿa)</t>
+  </si>
+  <si>
     <t>Hussein Yahfoufi</t>
   </si>
   <si>
@@ -178,6 +214,12 @@
     <t>4th Grade</t>
   </si>
   <si>
+    <t>Webelos - 4th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat TBD</t>
+  </si>
+  <si>
     <t>Ayman Ayash</t>
   </si>
   <si>
@@ -187,7 +229,7 @@
     <t>aayash@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>4th Grade patrol leader</t>
+    <t>4th Grade patrol leader (Name customizable in portal)</t>
   </si>
   <si>
     <t>Mahdi Hammoud</t>
@@ -214,6 +256,12 @@
     <t>5th Grade</t>
   </si>
   <si>
+    <t>Arrow of Light - 5th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Amīr al-Muʾminīn (ʿa)</t>
+  </si>
+  <si>
     <t>Tamer Safwan</t>
   </si>
   <si>
@@ -250,6 +298,12 @@
     <t>6th Grade</t>
   </si>
   <si>
+    <t>Patrol 1 - 6th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat ʿIshāq al-Ḥusayn (ʿa)</t>
+  </si>
+  <si>
     <t>Mohamad Jalloul</t>
   </si>
   <si>
@@ -277,6 +331,12 @@
     <t>7th Grade</t>
   </si>
   <si>
+    <t>Patrol 2 - 6th/7th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Abū al-Faḍl al-ʿAbbās</t>
+  </si>
+  <si>
     <t>Hassan Issa</t>
   </si>
   <si>
@@ -304,6 +364,12 @@
     <t>8th Grade</t>
   </si>
   <si>
+    <t>Patrol 3 - 8th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat al-Bāqir (ʿa)</t>
+  </si>
+  <si>
     <t>Hasan Yahfoufi</t>
   </si>
   <si>
@@ -331,6 +397,12 @@
     <t>9th Grade</t>
   </si>
   <si>
+    <t>Patrol 4 - 9th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Asadullāh (ʿa)</t>
+  </si>
+  <si>
     <t>Mustapha Mourtada</t>
   </si>
   <si>
@@ -344,6 +416,12 @@
   </si>
   <si>
     <t>10th / 11th Grade</t>
+  </si>
+  <si>
+    <t>Patrol 5 - 10th/11th</t>
+  </si>
+  <si>
+    <t>Ṭalīʿat Abā ʿAbdillāh (ʿa)</t>
   </si>
   <si>
     <t>Mustapha Choucair</t>
@@ -387,7 +465,7 @@
     </font>
     <font>
       <i/>
-      <color rgb="FF1E293B"/>
+      <color rgb="FF123C2D"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -398,13 +476,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF0F172A"/>
+      <color rgb="FF17201C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF1D4ED8"/>
+      <color rgb="FF123C2D"/>
       <sz val="10.5"/>
       <name val="Consolas"/>
     </font>
@@ -424,17 +502,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E3A8A"/>
+        <fgColor rgb="FF123C2D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
+        <fgColor rgb="FFF7F2E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2563EB"/>
+        <fgColor rgb="FFB99645"/>
       </patternFill>
     </fill>
     <fill>
@@ -444,7 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="FFFDFBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -467,7 +545,7 @@
         <color rgb="FF94A3B8"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF1E3A8A"/>
+        <color rgb="FF123C2D"/>
       </bottom>
       <diagonal/>
     </border>
@@ -864,19 +942,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,8 +966,10 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -899,8 +980,10 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -925,635 +1008,785 @@
       <c r="H3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7">
+        <v>124</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="11">
+        <v>124</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7">
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="11">
+        <v>11</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="7">
+        <v>11</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="11">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="J9" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="7">
+        <v>10</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="11">
+        <v>10</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="7">
+        <v>10</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="11">
+        <v>15</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="7">
+        <v>15</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="11">
+        <v>15</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="7">
+        <v>14</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="11">
+        <v>14</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="7">
+        <v>14</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" s="11">
+        <v>12</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="7">
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="11">
+        <v>13</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="7">
+        <v>13</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I23" s="11">
+        <v>8</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="7">
+        <v>8</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I25" s="11">
+        <v>9</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I26" s="7">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7">
-        <v>124</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="J26" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I27" s="11">
         <v>11</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="11">
-        <v>124</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="7">
-        <v>12</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="11">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="7">
-        <v>11</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="11">
-        <v>10</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" s="7">
-        <v>10</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="11">
-        <v>10</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="7">
-        <v>10</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="11">
-        <v>15</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="7">
-        <v>15</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="11">
-        <v>15</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="7">
-        <v>14</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="11">
-        <v>14</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="7">
-        <v>14</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="11">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G20" s="7">
-        <v>12</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" s="11">
-        <v>13</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="7">
-        <v>13</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G23" s="11">
-        <v>8</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="G24" s="7">
-        <v>8</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="11">
-        <v>9</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="7">
-        <v>11</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G27" s="11">
-        <v>11</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>114</v>
+      <c r="J27" s="8" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/public/Dhulfiqar_Scouts_Leader_Logins.xlsx
+++ b/public/Dhulfiqar_Scouts_Leader_Logins.xlsx
@@ -4,22 +4,27 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Leader &amp; Ṭalīʿah Logins" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Leader &amp; Ṭalīʿah Directory" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Admin Support &amp; Recovery" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="WhatsApp Quick-Start Guide" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="144">
-  <si>
-    <t>⚜️ Dhulfiqār Scouts — Leader &amp; Ṭalīʿah (Group) Login Credentials</t>
-  </si>
-  <si>
-    <t>Universal Mobile App: http://localhost:5173 | Default Password for All Accounts: scouts2026</t>
-  </si>
-  <si>
-    <t>Grade / Patrol Unit</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="202">
+  <si>
+    <t>⚜️ DHULFIQĀR SCOUTS — 2026–2027 MASTER LEADER &amp; ṬALĪʿAH DIRECTORY</t>
+  </si>
+  <si>
+    <t>📲 Live App: https://scout-tracker-tau.vercel.app/   |   🔑 Initial Password: scouts2026   |   Total Registered Scouts: 124</t>
+  </si>
+  <si>
+    <t>🛡️ DEDICATED ADMIN SUPPORT &amp; PASSWORD RECOVERY CONTACTS:  [1] Troop Leader (@leader - leader@dhulfiqarscouts.org)  •  [2] Troop Admin (@admin - admin@dhulfiqarscouts.org)</t>
+  </si>
+  <si>
+    <t>Grade / Unit</t>
   </si>
   <si>
     <t>Ṭalīʿah Rank</t>
@@ -28,7 +33,7 @@
     <t>Ṭalīʿah Group Name</t>
   </si>
   <si>
-    <t>Role</t>
+    <t>Leadership Role</t>
   </si>
   <si>
     <t>Full Name</t>
@@ -37,16 +42,19 @@
     <t>Username</t>
   </si>
   <si>
-    <t>Password</t>
+    <t>Initial Password</t>
   </si>
   <si>
     <t>Firebase Email</t>
   </si>
   <si>
-    <t>Assigned Scouts</t>
-  </si>
-  <si>
-    <t>Notes &amp; Scope</t>
+    <t>Scouts</t>
+  </si>
+  <si>
+    <t>Password Support Admin</t>
+  </si>
+  <si>
+    <t>Notes &amp; Permissions</t>
   </si>
   <si>
     <t>All Units (Admin)</t>
@@ -58,7 +66,7 @@
     <t>All Troop Units (11 Ṭalāʾiʿ)</t>
   </si>
   <si>
-    <t>Admin</t>
+    <t>Troop Leader (Admin)</t>
   </si>
   <si>
     <t>Troop Leader</t>
@@ -73,7 +81,13 @@
     <t>leader@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>Full admin access to all grades, ṭalāʾiʿ &amp; sessions</t>
+    <t>Self (Admin Support 1)</t>
+  </si>
+  <si>
+    <t>Full troop master access; oversees all 11 ṭalāʾiʿ &amp; provides password recovery support</t>
+  </si>
+  <si>
+    <t>Troop Admin (Admin)</t>
   </si>
   <si>
     <t>Troop Admin</t>
@@ -85,6 +99,12 @@
     <t>admin@dhulfiqarscouts.org</t>
   </si>
   <si>
+    <t>Self (Admin Support 2)</t>
+  </si>
+  <si>
+    <t>Technical administrator; manages database, user provisioning &amp; password reset service</t>
+  </si>
+  <si>
     <t>Kindergarten</t>
   </si>
   <si>
@@ -94,7 +114,7 @@
     <t>Ṭalīʿat al-Mahdi (ʿaj)</t>
   </si>
   <si>
-    <t>Leader</t>
+    <t>Patrol Leader</t>
   </si>
   <si>
     <t>Bilal Dabaja</t>
@@ -106,7 +126,10 @@
     <t>bdabaja@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>Kindergarten patrol leader</t>
+    <t>admin@dhulfiqarscouts.org / leader@dhulfiqarscouts.org</t>
+  </si>
+  <si>
+    <t>Kindergarten patrol leader; manages attendance &amp; star awards</t>
   </si>
   <si>
     <t>1st Grade</t>
@@ -127,7 +150,7 @@
     <t>nchamseddine@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>1st Grade patrol leader</t>
+    <t>1st Grade unit leader; manages check-ins &amp; duty rotations</t>
   </si>
   <si>
     <t>Assistant Leader</t>
@@ -142,7 +165,7 @@
     <t>msoueidan@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>1st Grade assistant leader</t>
+    <t>1st Grade assistant leader; co-manages attendance &amp; roster</t>
   </si>
   <si>
     <t>2nd Grade</t>
@@ -229,7 +252,7 @@
     <t>aayash@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>4th Grade patrol leader (Name customizable in portal)</t>
+    <t>4th Grade patrol leader (Ṭalīʿah name customizable in Portal)</t>
   </si>
   <si>
     <t>Mahdi Hammoud</t>
@@ -433,7 +456,7 @@
     <t>mchoucair@dhulfiqarscouts.org</t>
   </si>
   <si>
-    <t>Combined 10th &amp; 11th Grade unit leader</t>
+    <t>Combined senior unit leader</t>
   </si>
   <si>
     <t>Ali Harajli</t>
@@ -443,13 +466,166 @@
   </si>
   <si>
     <t>aharajli@dhulfiqarscouts.org</t>
+  </si>
+  <si>
+    <t>🛡️ ADMIN PROTOCOL: PASSWORD RECOVERY &amp; LEADER SUPPORT WORKFLOW</t>
+  </si>
+  <si>
+    <t>Designated Support Administrators: Troop Leader (@leader) &amp; Troop Admin (@admin)</t>
+  </si>
+  <si>
+    <t>Admin Role</t>
+  </si>
+  <si>
+    <t>Firebase Auth Email</t>
+  </si>
+  <si>
+    <t>Support Scope</t>
+  </si>
+  <si>
+    <t>Direct WhatsApp / Help Desk</t>
+  </si>
+  <si>
+    <t>Troop Leader (Command)</t>
+  </si>
+  <si>
+    <t>@leader</t>
+  </si>
+  <si>
+    <t>Program Oversight, Grade Allocations &amp; Emergency Password Resets</t>
+  </si>
+  <si>
+    <t>Available via Troop Leadership WhatsApp Channel</t>
+  </si>
+  <si>
+    <t>Troop Admin (Technical &amp; Operations)</t>
+  </si>
+  <si>
+    <t>@admin</t>
+  </si>
+  <si>
+    <t>Firebase Database, Portal Access, Password Recovery &amp; Technical Troubleshooting</t>
+  </si>
+  <si>
+    <t>📋 STEP-BY-STEP LEADER PASSWORD RECOVERY PROCEDURE (FOR ADMINS):</t>
+  </si>
+  <si>
+    <t>Step 1: Verify Identity</t>
+  </si>
+  <si>
+    <t>Leader contacts @leader or @admin requesting a password reset if they forgot their custom password.</t>
+  </si>
+  <si>
+    <t>Confirm the leader's full name, grade unit, and username in Sheet 1.</t>
+  </si>
+  <si>
+    <t>Step 2: Firebase Console Reset</t>
+  </si>
+  <si>
+    <t>Admin opens Google Firebase Console -&gt; Authentication -&gt; Users tab.</t>
+  </si>
+  <si>
+    <t>Search the leader's email (e.g. bdabaja@dhulfiqarscouts.org), click the 3 dots menu, and select "Reset Password" or set temporary password.</t>
+  </si>
+  <si>
+    <t>Step 3: In-App Portal Reset</t>
+  </si>
+  <si>
+    <t>Admin logs into https://scout-tracker-tau.vercel.app/ as @admin or @leader.</t>
+  </si>
+  <si>
+    <t>Navigate to ⚙️ Portal -&gt; Leader Accounts -&gt; Locate Leader -&gt; Click "Reset to Default (scouts2026)".</t>
+  </si>
+  <si>
+    <t>Step 4: Notify Leader &amp; Change</t>
+  </si>
+  <si>
+    <t>Leader logs in with default password scouts2026.</t>
+  </si>
+  <si>
+    <t>Leader goes to ⚙️ Portal -&gt; "Security &amp; Password Management" to set their new private password.</t>
+  </si>
+  <si>
+    <t>📲 WHATSAPP BROADCAST MESSAGE TEMPLATE FOR LEADERS</t>
+  </si>
+  <si>
+    <t>⚜️ DHULFIQĀR SCOUT TRACKER — LEADER ONBOARDING &amp; SETUP GUIDE ⚜️</t>
+  </si>
+  <si>
+    <t>Salam Alaykum Leaders! 🌲</t>
+  </si>
+  <si>
+    <t>We are excited to launch the official Dhulfiqār Scout Tracker app for our 2026–2027 scouting year.</t>
+  </si>
+  <si>
+    <t>📲 APP LINK: https://scout-tracker-tau.vercel.app/</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>📱 STEP 1: INSTALL ON YOUR PHONE (ADD TO HOME SCREEN)</t>
+  </si>
+  <si>
+    <t>🍏 For iPhone / iPad users (MUST use Safari):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1. Open link in Safari -&gt; Tap Share (square with arrow ⬆️) -&gt; Tap "Add to Home Screen" -&gt; Tap Add.</t>
+  </si>
+  <si>
+    <t>🤖 For Android users (MUST use Chrome):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1. Open link in Chrome -&gt; Tap 3 dots (⋮) -&gt; Tap "Install app" or "Add to Home screen" -&gt; Tap Install.</t>
+  </si>
+  <si>
+    <t>🔑 STEP 2: HOW TO LOG IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1. Select your name &amp; Ṭalīʿah in the dropdown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2. Initial Default Password: scouts2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   3. Tap Sign In.</t>
+  </si>
+  <si>
+    <t>🔒 STEP 3: CHANGE YOUR PASSWORD (MANDATORY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   1. Go to ⚙️ Portal tab -&gt; "Security &amp; Password Management".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   2. Enter current password (scouts2026) -&gt; Enter new private password -&gt; Tap Update Password.</t>
+  </si>
+  <si>
+    <t>🧪 STEP 4: PRACTICE WITH TEST 1 &amp; TEST 2 SANDBOXES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Test 1 (2026-09-25): Practice Check-In (Present / Absent / Excused).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Test 2 (2026-09-28): Practice Star Ratings in 🛡️ Duties &amp; Point Adjustments in 👥 Roster.</t>
+  </si>
+  <si>
+    <t>🛡️ PASSWORD RECOVERY &amp; ADMIN SUPPORT:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   If you ever forget your password or need assistance, please message our 2 Troop Admins:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Troop Leader: leader@dhulfiqarscouts.org (@leader)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • Troop Admin: admin@dhulfiqarscouts.org (@admin)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -464,6 +640,82 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF123C2D"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF92400E"/>
+      <sz val="9.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF123C2D"/>
+      <sz val="9.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F766E"/>
+      <sz val="9.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF166534"/>
+      <sz val="9.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F172A"/>
+      <sz val="9.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E40AF"/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB91C1C"/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF92400E"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF1E293B"/>
+      <sz val="9.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <i/>
       <color rgb="FF123C2D"/>
       <sz val="10"/>
@@ -472,28 +724,33 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E40AF"/>
+      <sz val="9.5"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF123C2D"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF17201C"/>
-      <sz val="10"/>
+      <b/>
+      <color rgb="FF1D4ED8"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="FF123C2D"/>
-      <sz val="10.5"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFB91C1C"/>
-      <sz val="10.5"/>
-      <name val="Consolas"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -512,7 +769,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB99645"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0FDF4"/>
       </patternFill>
     </fill>
     <fill>
@@ -522,7 +789,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDFBF7"/>
+        <fgColor rgb="FFFAF8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -536,13 +818,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF94A3B8"/>
+        <color rgb="FFD4AF37"/>
       </left>
       <right style="thin">
-        <color rgb="FF94A3B8"/>
+        <color rgb="FFD4AF37"/>
       </right>
-      <top style="thin">
-        <color rgb="FF94A3B8"/>
+      <top style="medium">
+        <color rgb="FF123C2D"/>
       </top>
       <bottom style="medium">
         <color rgb="FF123C2D"/>
@@ -568,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -576,33 +858,120 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,6 +987,50 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>64000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>34000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="714375" cy="714375"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -942,24 +1355,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="46" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="34" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -968,12 +1383,12 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -982,811 +1397,1399 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="6" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="E6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="7">
+      <c r="G6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="12">
         <v>124</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="H7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="12">
+        <v>124</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="22">
         <v>12</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="J8" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="32">
+        <v>11</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="22">
+        <v>11</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="32">
+        <v>10</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="22">
+        <v>10</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="I13" s="32">
+        <v>10</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="22">
+        <v>10</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="32">
+        <v>15</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="22">
+        <v>15</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17" s="32">
+        <v>15</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="22">
+        <v>14</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="32">
+        <v>14</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" s="22">
+        <v>14</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="I21" s="32">
+        <v>12</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" s="34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" s="22">
+        <v>12</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="I23" s="32">
         <v>13</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="J23" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" s="34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="22">
+        <v>13</v>
+      </c>
+      <c r="J24" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" s="24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="32">
+        <v>8</v>
+      </c>
+      <c r="J25" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" s="34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="I26" s="22">
+        <v>8</v>
+      </c>
+      <c r="J26" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="I27" s="32">
+        <v>9</v>
+      </c>
+      <c r="J27" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" s="34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" s="22">
+        <v>11</v>
+      </c>
+      <c r="J28" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" s="24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" ht="23" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F29" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="I29" s="32">
+        <v>11</v>
+      </c>
+      <c r="J29" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+    </row>
+    <row r="3" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="11">
-        <v>124</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="E5" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="7">
-        <v>12</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="11">
-        <v>11</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="7">
-        <v>11</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="11">
-        <v>10</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="7">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="11">
-        <v>10</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I12" s="7">
-        <v>10</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="11">
-        <v>15</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="7">
-        <v>15</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="11">
-        <v>15</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="7">
-        <v>14</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="11">
-        <v>14</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I18" s="7">
-        <v>14</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="I19" s="11">
-        <v>12</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I20" s="7">
-        <v>12</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="I21" s="11">
-        <v>13</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" s="7">
-        <v>13</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="11">
-        <v>8</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I24" s="7">
-        <v>8</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="I25" s="11">
-        <v>9</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I26" s="7">
-        <v>11</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" s="11">
-        <v>11</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>140</v>
-      </c>
+      <c r="E6" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+    </row>
+    <row r="10" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:G13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="2" max="5" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
